--- a/countries/es/1995-1999.xlsx
+++ b/countries/es/1995-1999.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>7201</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_ES_ECDC_AIDS_ANNUAL</t>
@@ -782,7 +787,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -792,6 +802,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -857,7 +872,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -872,22 +887,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -901,14 +916,39 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8764</v>
+        <v>7201</v>
       </c>
       <c r="O3" t="n">
-        <v>8764</v>
+        <v>7201</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,6 +956,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -923,16 +1021,26 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1013,17 +1121,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1042,14 +1150,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4599</v>
+        <v>8764</v>
       </c>
       <c r="O4" t="n">
-        <v>4599</v>
+        <v>8764</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1064,16 +1177,26 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1139,7 +1262,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1154,43 +1277,68 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6764</v>
+        <v>8764</v>
       </c>
       <c r="O5" t="n">
-        <v>6764</v>
+        <v>8764</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1198,6 +1346,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1205,16 +1411,26 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1295,17 +1511,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1315,23 +1531,28 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8331</v>
+        <v>4599</v>
       </c>
       <c r="O6" t="n">
-        <v>8331</v>
+        <v>4599</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1346,16 +1567,26 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1421,7 +1652,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1456,30 +1687,113 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3951</v>
+        <v>4599</v>
       </c>
       <c r="O7" t="n">
-        <v>3951</v>
+        <v>4599</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Gonorrhoea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1487,7 +1801,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1497,6 +1816,11 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1577,22 +1901,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1606,14 +1930,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>22</v>
+        <v>6764</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>6764</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1628,16 +1957,26 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1703,7 +2042,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1738,30 +2077,113 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4975</v>
+        <v>6764</v>
       </c>
       <c r="O9" t="n">
-        <v>4975</v>
+        <v>6764</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1769,7 +2191,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1779,6 +2206,11 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1879,19 +2311,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9347</v>
+        <v>8331</v>
       </c>
       <c r="O10" t="n">
-        <v>9347</v>
+        <v>8331</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1910,7 +2347,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1920,6 +2362,11 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1985,7 +2432,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2000,17 +2447,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2020,23 +2467,48 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2352</v>
+        <v>8331</v>
       </c>
       <c r="O11" t="n">
-        <v>2352</v>
+        <v>8331</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2044,6 +2516,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2051,16 +2581,26 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2141,17 +2681,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2161,23 +2701,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>3951</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>3951</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2192,16 +2737,26 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2267,7 +2822,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2282,43 +2837,68 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3750</v>
+        <v>3951</v>
       </c>
       <c r="O13" t="n">
-        <v>3750</v>
+        <v>3951</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Gonorrhoea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2326,6 +2906,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2333,16 +2971,26 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2423,17 +3071,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2443,23 +3091,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>9111</v>
+        <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>9111</v>
+        <v>22</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2474,16 +3127,26 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2549,7 +3212,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2564,17 +3227,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2584,23 +3247,48 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2608,6 +3296,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2615,16 +3361,26 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT15" t="n">
         <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2705,43 +3461,48 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2169</v>
+        <v>4975</v>
       </c>
       <c r="O16" t="n">
-        <v>2169</v>
+        <v>4975</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2756,16 +3517,26 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT16" t="n">
         <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2831,7 +3602,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2846,43 +3617,68 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4975</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4975</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2890,6 +3686,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2897,16 +3751,26 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2987,43 +3851,48 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3165</v>
+        <v>9347</v>
       </c>
       <c r="O18" t="n">
-        <v>3165</v>
+        <v>9347</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3038,16 +3907,26 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3113,7 +3992,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3128,43 +4007,68 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3172,6 +4076,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3179,16 +4141,26 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3269,17 +4241,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3289,23 +4261,28 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>8393</v>
+        <v>2352</v>
       </c>
       <c r="O20" t="n">
-        <v>8393</v>
+        <v>2352</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3320,16 +4297,26 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
         <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3395,7 +4382,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3410,17 +4397,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3430,23 +4417,48 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>220</v>
+        <v>2352</v>
       </c>
       <c r="O21" t="n">
-        <v>220</v>
+        <v>2352</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Gonorrhoea</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3454,6 +4466,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3461,16 +4531,26 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
         <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3551,17 +4631,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3571,23 +4651,28 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1467</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>1467</v>
+        <v>6</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3602,16 +4687,26 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3677,7 +4772,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3692,17 +4787,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3712,23 +4807,48 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>947</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>947</v>
+        <v>6</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3736,6 +4856,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3743,17 +4921,27 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
         <v>1</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -3790,6 +4978,4296 @@
         </is>
       </c>
       <c r="BC23" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3750</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3750</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3750</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3750</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>9111</v>
+      </c>
+      <c r="O26" t="n">
+        <v>9111</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>9111</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9111</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>106</v>
+      </c>
+      <c r="O28" t="n">
+        <v>106</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>106</v>
+      </c>
+      <c r="O29" t="n">
+        <v>106</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2169</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2169</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2169</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2169</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Gonorrhoea</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>3165</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3165</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>3165</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3165</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>8393</v>
+      </c>
+      <c r="O38" t="n">
+        <v>8393</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>8393</v>
+      </c>
+      <c r="O39" t="n">
+        <v>8393</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>220</v>
+      </c>
+      <c r="O40" t="n">
+        <v>220</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>220</v>
+      </c>
+      <c r="O41" t="n">
+        <v>220</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1467</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1467</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1467</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1467</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Gonorrhoea</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_GONO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>947</v>
+      </c>
+      <c r="O44" t="n">
+        <v>947</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>947</v>
+      </c>
+      <c r="O45" t="n">
+        <v>947</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Invasive meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -3921,7 +9399,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -3941,7 +9419,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -3951,7 +9429,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
